--- a/Testing-reportHW04_6810301028.xlsx
+++ b/Testing-reportHW04_6810301028.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my-homework_backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4378C0B8-F812-44E4-A69C-1A56868EF188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{8B8EA29B-22E5-427B-8AFD-B4791E457531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
     <sheet name="Env" sheetId="2" r:id="rId2"/>
     <sheet name="TC01" sheetId="3" r:id="rId3"/>
     <sheet name="TC02" sheetId="4" r:id="rId4"/>
-    <sheet name="TC03" sheetId="5" r:id="rId5"/>
-    <sheet name="TC04" sheetId="6" r:id="rId6"/>
+    <sheet name="TC04" sheetId="6" r:id="rId5"/>
+    <sheet name="TC03" sheetId="5" r:id="rId6"/>
     <sheet name="TC05" sheetId="7" r:id="rId7"/>
-    <sheet name="TestCaseTemplate" sheetId="9" r:id="rId8"/>
+    <sheet name="TC6" sheetId="10" r:id="rId8"/>
+    <sheet name="TestCaseTemplate" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Control!$A$1:$J$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Env!$A$1:$E$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'TC01'!$A$1:$I$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">TestCaseTemplate!$A$1:$I$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">TestCaseTemplate!$A$1:$I$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -211,14 +212,14 @@
           <commentPr defaultSize="0" autoFill="0" autoLine="0">
             <anchor>
               <from>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>160020</xdr:colOff>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>2110740</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>312420</xdr:colOff>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>601980</xdr:colOff>
                 <xdr:row>9</xdr:row>
                 <xdr:rowOff>68580</xdr:rowOff>
               </to>
@@ -296,14 +297,14 @@
           <commentPr defaultSize="0" autoFill="0" autoLine="0">
             <anchor>
               <from>
-                <xdr:col>14</xdr:col>
-                <xdr:colOff>167640</xdr:colOff>
+                <xdr:col>13</xdr:col>
+                <xdr:colOff>472440</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>16</xdr:col>
-                <xdr:colOff>320040</xdr:colOff>
+                <xdr:colOff>15240</xdr:colOff>
                 <xdr:row>9</xdr:row>
                 <xdr:rowOff>68580</xdr:rowOff>
               </to>
@@ -322,7 +323,7 @@
     <author>Sarayut Chaisuriya</author>
   </authors>
   <commentList>
-    <comment ref="I6" authorId="0" shapeId="5121" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="I6" authorId="0" shapeId="6145" xr:uid="{00000000-0006-0000-0500-000001000000}">
       <text>
         <r>
           <rPr>
@@ -387,8 +388,8 @@
                 <xdr:rowOff>45720</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>220980</xdr:colOff>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>411480</xdr:colOff>
                 <xdr:row>9</xdr:row>
                 <xdr:rowOff>68580</xdr:rowOff>
               </to>
@@ -407,7 +408,7 @@
     <author>Sarayut Chaisuriya</author>
   </authors>
   <commentList>
-    <comment ref="I6" authorId="0" shapeId="6145" xr:uid="{00000000-0006-0000-0500-000001000000}">
+    <comment ref="I6" authorId="0" shapeId="5121" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -567,8 +568,8 @@
                 <xdr:rowOff>45720</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>556260</xdr:colOff>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>2506980</xdr:colOff>
                 <xdr:row>9</xdr:row>
                 <xdr:rowOff>68580</xdr:rowOff>
               </to>
@@ -582,6 +583,101 @@
 </file>
 
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Sarayut Chaisuriya</author>
+  </authors>
+  <commentList>
+    <comment ref="I6" authorId="0" shapeId="9218" xr:uid="{FC25C79D-C874-49AD-88CD-4AD89DE2D9B8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sarayut Chaisuriya:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+-Search Command</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+-Stability test</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+-Performance Test</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+-Thai Grammar test</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+-Generic</t>
+        </r>
+      </text>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="v"/>
+        <mc:Fallback>
+          <commentPr defaultSize="0" autoFill="0" autoLine="0">
+            <anchor>
+              <from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>3208020</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>91440</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>4579620</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>114300</xdr:rowOff>
+              </to>
+            </anchor>
+          </commentPr>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Sarayut Chaisuriya</author>
@@ -677,7 +773,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="435" uniqueCount="148">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="496" uniqueCount="164">
   <si>
     <t>Test Report</t>
   </si>
@@ -1121,6 +1217,54 @@
   </si>
   <si>
     <t xml:space="preserve"> ช่อง StartRow แสดงเลข 50</t>
+  </si>
+  <si>
+    <t>https://github.com/Houngsakoun/Homework04_6810301028.git</t>
+  </si>
+  <si>
+    <t>TC06</t>
+  </si>
+  <si>
+    <t>Input Validation</t>
+  </si>
+  <si>
+    <t>เพื่อตรวจสอบว่าระบบบล็อกการพิมพ์ตัวอักษร และแจ้งเตือนได้อย่างถูกต้องในช่องระบุช่วงแถว</t>
+  </si>
+  <si>
+    <t>ทดสอบฟังก์ชันดักจับคีย์บอร์ด (KeyPress) ในช่อง TextBox ทั้ง 4 ช่อง (tbStartRow, tbEndRow, tbStartRowCsv, tbEndRowCsv) ว่ารับเฉพาะตัวเลข 0-9 และปุ่มควบคุมได้เท่านั้น</t>
+  </si>
+  <si>
+    <t>นำเคอร์เซอร์ไปคลิกที่ช่อง "StartRow" ฝั่ง Text (tbStartRow)</t>
+  </si>
+  <si>
+    <t>เคอร์เซอร์กะพริบอยู่ในช่อง พร้อมรับข้อมูล</t>
+  </si>
+  <si>
+    <t>พิมพ์ตัวอักษรภาษาอังกฤษ หรือภาษาไทยลงไป (เช่น cwc ตามภาพตัวอย่าง)</t>
+  </si>
+  <si>
+    <t>1. ตัวอักษรไม่ปรากฏลงในช่อง</t>
+  </si>
+  <si>
+    <t>2. มีหน้าต่างแจ้งเตือน (MessageBox) เด้งขึ้นมาพร้อมข้อความ "กรุณากรอกเฉพาะตัวเลข (0-9) เท่านั้นครับ"</t>
+  </si>
+  <si>
+    <t>ปิดหน้าต่างแจ้งเตือน แล้วพิมพ์ตัวเลขลงไป (เช่น 1, 5, 9)</t>
+  </si>
+  <si>
+    <t>ตัวเลขสามารถพิมพ์ลงในช่องได้ตามปกติ</t>
+  </si>
+  <si>
+    <t>กดปุ่ม Backspace (ปุ่มลบ) บนคีย์บอร์ด</t>
+  </si>
+  <si>
+    <t>สามารถกดลบตัวเลขในช่องได้ตามปกติ</t>
+  </si>
+  <si>
+    <t>ทำซ้ำขั้นตอนที่ 1-4 กับช่องที่เหลือ (tbEndRow, tbStartRowCsv, tbEndRowCsv)</t>
+  </si>
+  <si>
+    <t>ผลลัพธ์ต้องออกมาเหมือนกับขั้นตอนที่ 2-4 (รับแค่ตัวเลขและปุ่มควบคุม แจ้งเตือนเมื่อพิมพ์อักษร)</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1574,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1576,53 +1720,75 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1630,69 +1796,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1779,7 +1942,7 @@
             <xdr:cNvPr id="2049" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C333E74-05CD-4EF0-BEC6-4B657C98A3AC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31C4A1F4-3B65-49B9-A5FA-B249F8E687A0}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1892,7 +2055,7 @@
             <xdr:cNvPr id="2050" name="Comment 2" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EA82447-9DBC-4F33-92A6-58111CEB7AAF}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE044342-D945-4676-B726-43C835989070}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1994,14 +2157,14 @@
     <mc:Fallback>
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>160020</xdr:colOff>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>2110740</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>45720</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>312420</xdr:colOff>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>601980</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>68580</xdr:rowOff>
         </xdr:to>
@@ -2010,7 +2173,7 @@
             <xdr:cNvPr id="3073" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8FD2FD8-8734-4183-ADE8-4CE6912015DC}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DD5203D-7B1E-4C45-8AFE-F57F1DA8537D}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2199,14 +2362,14 @@
     <mc:Fallback>
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
-          <xdr:col>14</xdr:col>
-          <xdr:colOff>167640</xdr:colOff>
+          <xdr:col>13</xdr:col>
+          <xdr:colOff>472440</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>45720</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>16</xdr:col>
-          <xdr:colOff>320040</xdr:colOff>
+          <xdr:colOff>15240</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>68580</xdr:rowOff>
         </xdr:to>
@@ -2215,7 +2378,7 @@
             <xdr:cNvPr id="4097" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BA00A01-228C-4E34-90D6-43B18C7CBD16}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74992EED-38DD-4D9B-A91A-8D860E01BAAB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2373,7 +2536,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="logo3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8886AB46-C0EC-47A4-9754-39E7BEF43CA4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18487714-2030-4B90-9B46-8E489AE4DCE6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2410,17 +2573,17 @@
           <xdr:rowOff>45720</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>220980</xdr:colOff>
+          <xdr:col>9</xdr:col>
+          <xdr:colOff>411480</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>68580</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5121" name="Comment 1" hidden="1">
+            <xdr:cNvPr id="6145" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E75BEC9-E53A-4CC5-B5B6-550157797075}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAE75B24-21F3-423B-8F2E-7DACA32A16D3}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2567,7 +2730,7 @@
 <xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>742950</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2578,7 +2741,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="logo3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18487714-2030-4B90-9B46-8E489AE4DCE6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8886AB46-C0EC-47A4-9754-39E7BEF43CA4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2622,10 +2785,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6145" name="Comment 1" hidden="1">
+            <xdr:cNvPr id="5121" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{348F350B-F863-4997-A459-E118366729CB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE436D22-DCEE-4B18-AFF9-3CB2ACCB8436}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2772,7 +2935,7 @@
 <xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>742950</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2820,8 +2983,8 @@
           <xdr:rowOff>45720</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>556260</xdr:colOff>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>2506980</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>68580</xdr:rowOff>
         </xdr:to>
@@ -2830,7 +2993,7 @@
             <xdr:cNvPr id="7169" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3D13D0B-E993-47F3-AFD2-58F78D2C55E3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86043466-A892-4C5F-A9E4-8DD5C7E5F624}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2991,6 +3154,188 @@
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:v="urn:schemas-microsoft-com:vml" Requires="v"/>
+    <mc:Fallback>
+      <xdr:twoCellAnchor editAs="absolute">
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>3208020</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>91440</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>4579620</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>114300</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="9218" name="Comment 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9825E6A-87F4-4F5D-88F0-D3D1366F7736}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1">
+              <a:spLocks noChangeArrowheads="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="9456420" y="1013460"/>
+              <a:ext cx="1371600" cy="861060"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFE1" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="80"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="510000"/>
+              </a:solidFill>
+              <a:miter lim="800%"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+            <a:effectLst/>
+            <a:extLst>
+              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
+                <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                  <a:effectLst>
+                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
+                      <a:srgbClr val="510000"/>
+                    </a:outerShdw>
+                  </a:effectLst>
+                </a14:hiddenEffects>
+              </a:ext>
+              <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
+                <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="1"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="0" bIns="0" anchor="t" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0%">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma"/>
+                  <a:ea typeface="Tahoma"/>
+                  <a:cs typeface="Tahoma"/>
+                </a:rPr>
+                <a:t>Sarayut Chaisuriya:</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Tahoma"/>
+                <a:ea typeface="Tahoma"/>
+                <a:cs typeface="Tahoma"/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma"/>
+                  <a:ea typeface="Tahoma"/>
+                  <a:cs typeface="Tahoma"/>
+                </a:rPr>
+                <a:t>-Search Command</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma"/>
+                  <a:ea typeface="Tahoma"/>
+                  <a:cs typeface="Tahoma"/>
+                </a:rPr>
+                <a:t>-Stability test</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma"/>
+                  <a:ea typeface="Tahoma"/>
+                  <a:cs typeface="Tahoma"/>
+                </a:rPr>
+                <a:t>-Performance Test</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma"/>
+                  <a:ea typeface="Tahoma"/>
+                  <a:cs typeface="Tahoma"/>
+                </a:rPr>
+                <a:t>-Thai Grammar test</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma"/>
+                  <a:ea typeface="Tahoma"/>
+                  <a:cs typeface="Tahoma"/>
+                </a:rPr>
+                <a:t>-Generic</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Fallback>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
@@ -3051,7 +3396,7 @@
             <xdr:cNvPr id="8193" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{996E928B-3A73-4CC9-9344-6B46BCC945DE}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{104C6750-B4C8-439D-87C3-E4AF69FE3AC4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3518,23 +3863,23 @@
     <col min="6" max="6" width="12.21875" customWidth="1"/>
     <col min="7" max="7" width="16.88671875" customWidth="1"/>
     <col min="8" max="9" width="5" customWidth="1"/>
-    <col min="10" max="10" width="29" customWidth="1"/>
+    <col min="10" max="10" width="33.33203125" customWidth="1"/>
     <col min="11" max="11" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="2" t="s">
-        <v>1</v>
+      <c r="J1" s="109" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -3544,20 +3889,20 @@
       <c r="B2" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="70"/>
+      <c r="D2" s="67"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70" t="s">
+      <c r="G2" s="67"/>
+      <c r="H2" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -3575,10 +3920,10 @@
         <v>10</v>
       </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="71" t="s">
+      <c r="H3" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="71"/>
+      <c r="I3" s="68"/>
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -3592,17 +3937,17 @@
         <v>7</v>
       </c>
       <c r="D4" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="9" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="11"/>
-      <c r="H4" s="68" t="s">
+      <c r="H4" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="68"/>
+      <c r="I4" s="65"/>
       <c r="J4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3625,42 +3970,42 @@
       <c r="G5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="66" t="s">
+      <c r="H5" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="66"/>
+      <c r="I5" s="69"/>
       <c r="J5" s="14" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67" t="s">
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="67" t="s">
+      <c r="F6" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67" t="s">
+      <c r="G6" s="70"/>
+      <c r="H6" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="67"/>
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="67"/>
+      <c r="A7" s="70"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
       <c r="F7" s="17" t="s">
         <v>27</v>
       </c>
@@ -3681,12 +4026,12 @@
       <c r="A8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="62" t="str">
+      <c r="B8" s="71" t="str">
         <f>'TC01'!B6</f>
         <v>Load_Data_Range_CSV</v>
       </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
       <c r="E8" s="19" t="s">
         <v>33</v>
       </c>
@@ -3700,12 +4045,12 @@
       <c r="A9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="63" t="str">
+      <c r="B9" s="72" t="str">
         <f>'TC02'!B6</f>
         <v>Invalid_Range_Validation</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
       <c r="E9" s="19" t="s">
         <v>33</v>
       </c>
@@ -3719,12 +4064,12 @@
       <c r="A10" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="63" t="str">
+      <c r="B10" s="72" t="str">
         <f>'TC03'!B6</f>
         <v>Data_Filtering_Exe</v>
       </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
       <c r="E10" s="19" t="s">
         <v>33</v>
       </c>
@@ -3738,12 +4083,12 @@
       <c r="A11" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="63" t="str">
+      <c r="B11" s="72" t="str">
         <f>'TC04'!B6</f>
         <v>Read_As_Text_UI_Test</v>
       </c>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
       <c r="E11" s="19" t="s">
         <v>33</v>
       </c>
@@ -3757,11 +4102,11 @@
       <c r="A12" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
       <c r="E12" s="28" t="s">
         <v>33</v>
       </c>
@@ -3772,10 +4117,12 @@
       <c r="J12" s="27"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
+      <c r="A13" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
       <c r="E13" s="28"/>
       <c r="F13" s="24"/>
       <c r="G13" s="5"/>
@@ -3785,9 +4132,9 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="28"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
       <c r="E14" s="28"/>
       <c r="F14" s="24"/>
       <c r="G14" s="5"/>
@@ -3797,9 +4144,9 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
       <c r="E15" s="28"/>
       <c r="F15" s="24"/>
       <c r="G15" s="5"/>
@@ -3809,9 +4156,9 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
-      <c r="B16" s="65"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
       <c r="E16" s="28"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -3821,9 +4168,9 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
-      <c r="B17" s="65"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
       <c r="E17" s="28"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -3833,9 +4180,9 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="28"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
       <c r="E18" s="28"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -3845,9 +4192,9 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="28"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
       <c r="E19" s="28"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -3857,9 +4204,9 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="28"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
       <c r="E20" s="28"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -3869,9 +4216,9 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
       <c r="E21" s="29"/>
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
@@ -3883,10 +4230,10 @@
       <c r="A22" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="60" t="s">
+      <c r="B22" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="60"/>
+      <c r="C22" s="76"/>
       <c r="G22" s="34" t="s">
         <v>40</v>
       </c>
@@ -3903,89 +4250,85 @@
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="61"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="77"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="59"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="75"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="75"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="75"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="59"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="75"/>
     </row>
     <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="59"/>
-      <c r="C28" s="59"/>
-      <c r="D28" s="59"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
       <c r="F28" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
+      <c r="G28" s="75"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:D10"/>
@@ -4000,14 +4343,18 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -4033,21 +4380,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="80" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="77"/>
+      <c r="C2" s="80"/>
       <c r="D2" s="34" t="s">
         <v>44</v>
       </c>
@@ -4059,8 +4406,8 @@
       <c r="A3" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
       <c r="D3" s="34" t="s">
         <v>45</v>
       </c>
@@ -4072,10 +4419,10 @@
       <c r="A4" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="72" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="63"/>
+      <c r="C4" s="72"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
@@ -4101,10 +4448,10 @@
       <c r="B6" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="75"/>
+      <c r="D6" s="78"/>
       <c r="E6" s="42"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -4112,10 +4459,10 @@
       <c r="B7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="75" t="s">
+      <c r="C7" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="75"/>
+      <c r="D7" s="78"/>
       <c r="E7" s="42"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -4123,8 +4470,8 @@
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
       <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -4132,8 +4479,8 @@
       <c r="B9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
       <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -4168,14 +4515,14 @@
       <c r="B13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
       <c r="E13" s="42"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="43"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
       <c r="E14" s="42"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -4185,10 +4532,10 @@
       <c r="B15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="75" t="s">
+      <c r="C15" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="75"/>
+      <c r="D15" s="78"/>
       <c r="E15" s="42"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -4196,8 +4543,8 @@
       <c r="B16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
       <c r="E16" s="42"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -4205,8 +4552,8 @@
       <c r="B17" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
       <c r="E17" s="42"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -4214,8 +4561,8 @@
       <c r="B18" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
       <c r="E18" s="42"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -4250,33 +4597,33 @@
       <c r="B22" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
       <c r="E22" s="42"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="47"/>
       <c r="B25" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="73" t="s">
+      <c r="C25" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="73"/>
+      <c r="D25" s="82"/>
       <c r="E25" s="48" t="s">
         <v>31</v>
       </c>
@@ -4285,22 +4632,22 @@
       <c r="A26" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="C26" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="65"/>
+      <c r="D26" s="74"/>
       <c r="E26" s="42"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="49"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="65"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
       <c r="E27" s="42"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="49"/>
-      <c r="C28" s="65"/>
-      <c r="D28" s="65"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="74"/>
       <c r="E28" s="42"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -4311,54 +4658,54 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="49"/>
-      <c r="C30" s="65"/>
-      <c r="D30" s="65"/>
+      <c r="C30" s="74"/>
+      <c r="D30" s="74"/>
       <c r="E30" s="42"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="65"/>
-      <c r="D31" s="65"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
       <c r="E31" s="42"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="49"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="65"/>
+      <c r="C32" s="74"/>
+      <c r="D32" s="74"/>
       <c r="E32" s="42"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="49"/>
-      <c r="C33" s="65"/>
-      <c r="D33" s="65"/>
+      <c r="C33" s="74"/>
+      <c r="D33" s="74"/>
       <c r="E33" s="42"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="49"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="65"/>
+      <c r="C34" s="74"/>
+      <c r="D34" s="74"/>
       <c r="E34" s="42"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="67" t="s">
+      <c r="A35" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="B35" s="67"/>
-      <c r="C35" s="67"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
+      <c r="B35" s="70"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="49"/>
       <c r="B36" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="73" t="s">
+      <c r="C36" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="73"/>
+      <c r="D36" s="82"/>
       <c r="E36" s="48" t="s">
         <v>31</v>
       </c>
@@ -4368,29 +4715,29 @@
         <v>63</v>
       </c>
       <c r="B37" s="42"/>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
+      <c r="C37" s="84"/>
+      <c r="D37" s="84"/>
       <c r="E37" s="42"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="49"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="72"/>
-      <c r="D38" s="72"/>
+      <c r="C38" s="84"/>
+      <c r="D38" s="84"/>
       <c r="E38" s="42"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="49"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="72"/>
-      <c r="D39" s="72"/>
+      <c r="C39" s="84"/>
+      <c r="D39" s="84"/>
       <c r="E39" s="42"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="49"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
+      <c r="C40" s="84"/>
+      <c r="D40" s="84"/>
       <c r="E40" s="42"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -4398,32 +4745,43 @@
         <v>64</v>
       </c>
       <c r="B41" s="42"/>
-      <c r="C41" s="72"/>
-      <c r="D41" s="72"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="84"/>
       <c r="E41" s="42"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="49"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="72"/>
-      <c r="D42" s="72"/>
+      <c r="C42" s="84"/>
+      <c r="D42" s="84"/>
       <c r="E42" s="42"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="51"/>
       <c r="B43" s="42"/>
-      <c r="C43" s="72"/>
-      <c r="D43" s="72"/>
+      <c r="C43" s="84"/>
+      <c r="D43" s="84"/>
       <c r="E43" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
@@ -4436,23 +4794,12 @@
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.75000000000000011" right="0.75000000000000011" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -4478,21 +4825,23 @@
     <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="20.77734375" customWidth="1"/>
     <col min="7" max="8" width="5.21875" customWidth="1"/>
-    <col min="9" max="9" width="28.44140625" customWidth="1"/>
+    <col min="9" max="9" width="33.109375" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="2"/>
+      <c r="I1" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -4501,19 +4850,19 @@
       <c r="B2" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70" t="s">
+      <c r="F2" s="67"/>
+      <c r="G2" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -4530,10 +4879,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="71"/>
+      <c r="H3" s="68"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4547,16 +4896,16 @@
         <v>7</v>
       </c>
       <c r="D4" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="68"/>
+      <c r="H4" s="65"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -4578,27 +4927,27 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="66" t="s">
+      <c r="G5" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="66"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="82" t="s">
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="82"/>
+      <c r="H6" s="86"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
@@ -4607,117 +4956,117 @@
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="59" t="s">
+      <c r="B9" s="75" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="59" t="s">
+      <c r="B11" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67" t="s">
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67" t="s">
+      <c r="F12" s="70"/>
+      <c r="G12" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67" t="s">
+      <c r="H12" s="70"/>
+      <c r="I12" s="70" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="67"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
       <c r="G13" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="67"/>
+      <c r="I13" s="70"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="44">
         <v>1</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79" t="s">
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="79"/>
+      <c r="F14" s="87"/>
       <c r="G14" t="s">
         <v>146</v>
       </c>
@@ -4728,15 +5077,15 @@
       <c r="A15" s="44">
         <v>2</v>
       </c>
-      <c r="B15" s="79" t="s">
+      <c r="B15" s="87" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79" t="s">
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="79"/>
+      <c r="F15" s="87"/>
       <c r="G15" t="s">
         <v>146</v>
       </c>
@@ -4747,15 +5096,15 @@
       <c r="A16" s="44">
         <v>3</v>
       </c>
-      <c r="B16" s="79" t="s">
+      <c r="B16" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79" t="s">
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87" t="s">
         <v>99</v>
       </c>
-      <c r="F16" s="79"/>
+      <c r="F16" s="87"/>
       <c r="G16" t="s">
         <v>146</v>
       </c>
@@ -4766,15 +5115,15 @@
       <c r="A17" s="44">
         <v>4</v>
       </c>
-      <c r="B17" s="79" t="s">
+      <c r="B17" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79" t="s">
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="79"/>
+      <c r="F17" s="87"/>
       <c r="G17" t="s">
         <v>146</v>
       </c>
@@ -4783,22 +5132,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -4829,26 +5178,26 @@
       <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
       <c r="E22" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
@@ -4863,6 +5212,29 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:I13"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -4875,29 +5247,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.19000000000000003" top="0.27" bottom="0.16000000000000003" header="0.27" footer="0.16000000000000003"/>
   <pageSetup paperSize="0" scale="90" fitToWidth="0" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -4923,22 +5272,22 @@
     <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="32.44140625" customWidth="1"/>
     <col min="7" max="8" width="5.21875" customWidth="1"/>
-    <col min="9" max="9" width="28.44140625" customWidth="1"/>
+    <col min="9" max="9" width="32.88671875" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="2" t="s">
-        <v>1</v>
+      <c r="I1" s="109" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -4948,19 +5297,19 @@
       <c r="B2" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="96"/>
-      <c r="E2" s="95" t="s">
+      <c r="D2" s="90"/>
+      <c r="E2" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="96"/>
-      <c r="G2" s="95" t="s">
+      <c r="F2" s="90"/>
+      <c r="G2" s="89" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="97"/>
-      <c r="I2" s="96"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="90"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -4977,10 +5326,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="98"/>
+      <c r="H3" s="92"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4993,15 +5342,17 @@
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="10">
+        <v>2</v>
+      </c>
       <c r="E4" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="99"/>
+      <c r="H4" s="93"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -5023,27 +5374,27 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="66" t="s">
+      <c r="G5" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="100"/>
+      <c r="H5" s="94"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="101" t="s">
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="101"/>
+      <c r="H6" s="95"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
@@ -5052,127 +5403,127 @@
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="81" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="81" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="78"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="59" t="s">
+      <c r="B12" s="75" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="84" t="s">
+      <c r="A13" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="98" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="87"/>
-      <c r="D13" s="88"/>
-      <c r="E13" s="86" t="s">
+      <c r="C13" s="99"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="98" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="88"/>
-      <c r="G13" s="92" t="s">
+      <c r="F13" s="100"/>
+      <c r="G13" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="93"/>
-      <c r="I13" s="84" t="s">
+      <c r="H13" s="105"/>
+      <c r="I13" s="96" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="85"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="89"/>
-      <c r="F14" s="91"/>
+      <c r="A14" s="97"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="103"/>
       <c r="G14" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="85"/>
+      <c r="I14" s="97"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
-      <c r="B15" s="83" t="s">
+      <c r="B15" s="106" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="78"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="83" t="s">
+      <c r="C15" s="81"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="106" t="s">
         <v>106</v>
       </c>
-      <c r="F15" s="75"/>
+      <c r="F15" s="78"/>
       <c r="G15" t="s">
         <v>146</v>
       </c>
@@ -5183,15 +5534,15 @@
       <c r="A16" s="44">
         <v>2</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="106" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="78"/>
-      <c r="D16" s="75"/>
-      <c r="E16" s="83" t="s">
+      <c r="C16" s="81"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="106" t="s">
         <v>147</v>
       </c>
-      <c r="F16" s="75"/>
+      <c r="F16" s="78"/>
       <c r="G16" t="s">
         <v>146</v>
       </c>
@@ -5202,15 +5553,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="83" t="s">
+      <c r="B17" s="106" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83" t="s">
+      <c r="C17" s="106"/>
+      <c r="D17" s="106"/>
+      <c r="E17" s="106" t="s">
         <v>109</v>
       </c>
-      <c r="F17" s="83"/>
+      <c r="F17" s="106"/>
       <c r="G17" t="s">
         <v>146</v>
       </c>
@@ -5221,15 +5572,15 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="83" t="s">
+      <c r="B18" s="106" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="78"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="83" t="s">
+      <c r="C18" s="81"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="106" t="s">
         <v>110</v>
       </c>
-      <c r="F18" s="75"/>
+      <c r="F18" s="78"/>
       <c r="G18" t="s">
         <v>146</v>
       </c>
@@ -5238,11 +5589,11 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="94"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="94"/>
-      <c r="F19" s="74"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="83"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -5273,46 +5624,46 @@
       <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
       <c r="E22" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -5327,6 +5678,30 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="B9:I9"/>
@@ -5341,30 +5716,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -5381,8 +5732,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I27"/>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -5392,22 +5743,22 @@
     <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="31" customWidth="1"/>
     <col min="7" max="8" width="5.21875" customWidth="1"/>
-    <col min="9" max="9" width="28.44140625" customWidth="1"/>
+    <col min="9" max="9" width="34.5546875" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="2" t="s">
-        <v>1</v>
+      <c r="I1" s="109" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -5415,29 +5766,27 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="70" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70" t="s">
+      <c r="F2" s="67"/>
+      <c r="G2" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
         <v>9</v>
       </c>
@@ -5448,10 +5797,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="71"/>
+      <c r="H3" s="68"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5459,20 +5808,22 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="10">
+        <v>2</v>
+      </c>
       <c r="E4" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="68"/>
+      <c r="H4" s="65"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -5480,7 +5831,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>15</v>
@@ -5494,27 +5845,27 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="66" t="s">
+      <c r="G5" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="66"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="78" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="82" t="s">
+      <c r="B6" s="81" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="86" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="82"/>
+      <c r="H6" s="86"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
@@ -5523,127 +5874,127 @@
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="78" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
+      <c r="B7" s="81" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="78" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
+      <c r="B9" s="81" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67" t="s">
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67" t="s">
+      <c r="F13" s="70"/>
+      <c r="G13" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67" t="s">
+      <c r="H13" s="70"/>
+      <c r="I13" s="70" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="67"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
+      <c r="A14" s="70"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
       <c r="G14" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="67"/>
+      <c r="I14" s="70"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
-      <c r="B15" s="102" t="s">
-        <v>116</v>
-      </c>
-      <c r="C15" s="102"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="102" t="s">
-        <v>117</v>
-      </c>
-      <c r="F15" s="102"/>
+      <c r="B15" s="108" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="108"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="108"/>
       <c r="G15" t="s">
         <v>146</v>
       </c>
@@ -5654,15 +6005,15 @@
       <c r="A16" s="44">
         <v>2</v>
       </c>
-      <c r="B16" s="102" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="102" t="s">
-        <v>119</v>
-      </c>
-      <c r="F16" s="102"/>
+      <c r="B16" s="108" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="108"/>
       <c r="G16" t="s">
         <v>146</v>
       </c>
@@ -5673,15 +6024,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="72" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="F17" s="72"/>
+      <c r="B17" s="108" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
+      <c r="E17" s="108" t="s">
+        <v>129</v>
+      </c>
+      <c r="F17" s="108"/>
       <c r="G17" t="s">
         <v>146</v>
       </c>
@@ -5689,107 +6040,128 @@
       <c r="I17" s="44"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="44"/>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="4"/>
+      <c r="A18" s="44">
+        <v>4</v>
+      </c>
+      <c r="B18" s="108" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="108"/>
+      <c r="D18" s="108"/>
+      <c r="E18" s="108" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="108"/>
+      <c r="G18" t="s">
+        <v>146</v>
+      </c>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="44"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="44"/>
-    </row>
-    <row r="20" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F20" s="3" t="s">
+    <row r="19" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G20" s="56">
-        <f>COUNTA(G15:G19)</f>
-        <v>3</v>
-      </c>
-      <c r="H20" s="56">
-        <f>COUNTA(H15:H19)</f>
+      <c r="G19" s="56">
+        <f>COUNTA(G15:G18)</f>
+        <v>4</v>
+      </c>
+      <c r="H19" s="56">
+        <f>COUNTA(H15:H18)</f>
         <v>0</v>
       </c>
     </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="3"/>
+    </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="3"/>
+      <c r="A21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="77"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
+      <c r="E21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-    </row>
-    <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="58" t="s">
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+    </row>
+    <row r="25" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="58" t="s">
+      <c r="E25" s="58" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="36">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -5802,488 +6174,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
-  <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
-  <drawing r:id="rId2"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="v">
-      <legacyDrawing r:id="rId3"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
-    <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="8" width="5.21875" customWidth="1"/>
-    <col min="9" max="9" width="28.44140625" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="81" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="70" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="7" t="d">
-        <v>2026-06-30</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="71"/>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="68" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="68"/>
-      <c r="I4" s="11"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="66" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="66"/>
-      <c r="I5" s="54"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="78" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="82" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="82"/>
-      <c r="I6" s="55" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="78" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="78" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="78"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="78" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="67" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="67" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="67"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="67"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="44">
-        <v>1</v>
-      </c>
-      <c r="B15" s="102" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" s="102"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="102" t="s">
-        <v>125</v>
-      </c>
-      <c r="F15" s="102"/>
-      <c r="G15" t="s">
-        <v>146</v>
-      </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="44"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="44">
-        <v>2</v>
-      </c>
-      <c r="B16" s="102" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="102" t="s">
-        <v>127</v>
-      </c>
-      <c r="F16" s="102"/>
-      <c r="G16" t="s">
-        <v>146</v>
-      </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="44"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="44">
-        <v>3</v>
-      </c>
-      <c r="B17" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="102"/>
-      <c r="D17" s="102"/>
-      <c r="E17" s="102" t="s">
-        <v>129</v>
-      </c>
-      <c r="F17" s="102"/>
-      <c r="G17" t="s">
-        <v>146</v>
-      </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="44"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="44">
-        <v>4</v>
-      </c>
-      <c r="B18" s="102" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="102"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="102" t="s">
-        <v>131</v>
-      </c>
-      <c r="F18" s="102"/>
-      <c r="G18" t="s">
-        <v>146</v>
-      </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="44"/>
-    </row>
-    <row r="19" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="56">
-        <f>COUNTA(G15:G18)</f>
-        <v>4</v>
-      </c>
-      <c r="H19" s="56">
-        <f>COUNTA(H15:H18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="61"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
-    </row>
-    <row r="25" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="58" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="58" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -6298,9 +6188,474 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
+    <col min="7" max="8" width="5.21875" customWidth="1"/>
+    <col min="9" max="9" width="28.44140625" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="85" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="1"/>
+      <c r="J1" s="109" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="7" t="d">
+        <v>2026-06-30</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="68"/>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="10">
+        <v>2</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="65"/>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" s="69"/>
+      <c r="I5" s="54"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="81" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="86" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="86"/>
+      <c r="I6" s="55" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="81" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="81" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="81" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="70" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="70" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="70"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="70"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="44">
+        <v>1</v>
+      </c>
+      <c r="B15" s="108" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="108"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" s="108"/>
+      <c r="G15" t="s">
+        <v>146</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="44"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="44">
+        <v>2</v>
+      </c>
+      <c r="B16" s="108" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="108"/>
+      <c r="G16" t="s">
+        <v>146</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="44"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="44">
+        <v>3</v>
+      </c>
+      <c r="B17" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84" t="s">
+        <v>120</v>
+      </c>
+      <c r="F17" s="84"/>
+      <c r="G17" t="s">
+        <v>146</v>
+      </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="44"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="44"/>
+      <c r="B18" s="84"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="44"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="44"/>
+      <c r="B19" s="84"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="44"/>
+    </row>
+    <row r="20" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="56">
+        <f>COUNTA(G15:G19)</f>
+        <v>3</v>
+      </c>
+      <c r="H20" s="56">
+        <f>COUNTA(H15:H19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="E22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+    </row>
+    <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="58" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
+  <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <drawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="v">
+      <legacyDrawing r:id="rId3"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -6310,46 +6665,46 @@
     <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
     <col min="7" max="8" width="5.21875" customWidth="1"/>
-    <col min="9" max="9" width="28.44140625" customWidth="1"/>
+    <col min="9" max="9" width="37.109375" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="81" t="s">
+    <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="109" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70" t="s">
+      <c r="F2" s="67"/>
+      <c r="G2" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -6364,13 +6719,13 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="71"/>
+      <c r="H3" s="68"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -6380,18 +6735,20 @@
       <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="10">
+        <v>2</v>
+      </c>
       <c r="E4" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="68"/>
+      <c r="H4" s="65"/>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>72</v>
       </c>
@@ -6410,175 +6767,175 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="66" t="s">
+      <c r="G5" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="66"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="54"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="82" t="s">
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="86" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="82"/>
+      <c r="H6" s="86"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="78" t="s">
+      <c r="B7" s="81" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="81" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="75"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="81" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="67" t="s">
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67" t="s">
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67" t="s">
+      <c r="F13" s="70"/>
+      <c r="G13" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67" t="s">
+      <c r="H13" s="70"/>
+      <c r="I13" s="70" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="67"/>
-      <c r="B14" s="67"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="70"/>
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
       <c r="G14" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="67"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I14" s="70"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="108" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="102"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="102" t="s">
+      <c r="C15" s="108"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108" t="s">
         <v>136</v>
       </c>
-      <c r="F15" s="102"/>
+      <c r="F15" s="108"/>
       <c r="G15" t="s">
         <v>146</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="44"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="44">
         <v>2</v>
       </c>
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="108" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="102" t="s">
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108" t="s">
         <v>138</v>
       </c>
-      <c r="F16" s="102"/>
+      <c r="F16" s="108"/>
       <c r="G16" t="s">
         <v>146</v>
       </c>
@@ -6589,15 +6946,15 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="72" t="s">
+      <c r="B17" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72" t="s">
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84" t="s">
         <v>140</v>
       </c>
-      <c r="F17" s="72"/>
+      <c r="F17" s="84"/>
       <c r="G17" t="s">
         <v>146</v>
       </c>
@@ -6608,15 +6965,15 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72" t="s">
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84" t="s">
         <v>141</v>
       </c>
-      <c r="F18" s="72"/>
+      <c r="F18" s="84"/>
       <c r="G18" t="s">
         <v>146</v>
       </c>
@@ -6625,11 +6982,11 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
+      <c r="B19" s="84"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -6660,46 +7017,46 @@
       <c r="A22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
+      <c r="B22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
       <c r="E22" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
@@ -6714,32 +7071,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="B24:D24"/>
@@ -6752,9 +7083,35 @@
     <mergeCell ref="F22:I22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <drawing r:id="rId2"/>
@@ -6767,6 +7124,656 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85097F72-4E5C-4130-B248-600486E38418}">
+  <dimension ref="A1:J41"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" style="60" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" style="60" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" style="60" customWidth="1"/>
+    <col min="4" max="4" width="36.77734375" style="60" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" style="60" customWidth="1"/>
+    <col min="6" max="6" width="67.109375" style="60" customWidth="1"/>
+    <col min="7" max="8" width="5.21875" style="60" customWidth="1"/>
+    <col min="9" max="9" width="51.33203125" style="60" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="85" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="1"/>
+      <c r="J1" s="109" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="7" t="d">
+        <v>2026-06-30</v>
+      </c>
+      <c r="E3" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="68"/>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="10">
+        <v>2</v>
+      </c>
+      <c r="E4" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="65"/>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" s="69"/>
+      <c r="I5" s="54"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="75" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="86" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="86"/>
+      <c r="I6" s="55" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="64" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="75" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="75" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="64"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="64"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="64"/>
+      <c r="B12" s="75"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="64"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="64"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="75"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="64" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="81" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="70" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="70" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="70"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="70"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>1</v>
+      </c>
+      <c r="B19" s="84" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="84"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="84"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="44"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>2</v>
+      </c>
+      <c r="B20" s="84" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20" s="84"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="44"/>
+    </row>
+    <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="44"/>
+      <c r="B21" s="84"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="84" t="s">
+        <v>157</v>
+      </c>
+      <c r="F21" s="84"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="44"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>3</v>
+      </c>
+      <c r="B22" s="84" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="84"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="44"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>4</v>
+      </c>
+      <c r="B23" s="84" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" s="84"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="84" t="s">
+        <v>161</v>
+      </c>
+      <c r="F23" s="84"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="44"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>5</v>
+      </c>
+      <c r="B24" s="84" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="84"/>
+      <c r="D24" s="84"/>
+      <c r="E24" s="84" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24" s="84"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="44"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="44"/>
+      <c r="B25" s="84"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="84"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="44"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="44"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="44"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="44"/>
+      <c r="B27" s="84"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="44"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="44"/>
+      <c r="B28" s="84"/>
+      <c r="C28" s="84"/>
+      <c r="D28" s="84"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="44"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="44"/>
+      <c r="B29" s="84"/>
+      <c r="C29" s="84"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="44"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="44"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="84"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="44"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="44"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="84"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="44"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="44"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="44"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="44"/>
+      <c r="B33" s="84"/>
+      <c r="C33" s="84"/>
+      <c r="D33" s="84"/>
+      <c r="E33" s="84"/>
+      <c r="F33" s="84"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="44"/>
+    </row>
+    <row r="34" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F34" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="G34" s="56">
+        <f>COUNTA(G19:G33)</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="56">
+        <f>COUNTA(H19:H33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" s="64"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="77"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="60" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="64"/>
+      <c r="B37" s="75"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="75"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="75"/>
+      <c r="H37" s="75"/>
+      <c r="I37" s="75"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="64"/>
+      <c r="B38" s="75"/>
+      <c r="C38" s="75"/>
+      <c r="D38" s="75"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="75"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="75"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="64"/>
+      <c r="B39" s="75"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="75"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="75"/>
+    </row>
+    <row r="40" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="E40" s="58" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="62">
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="J1" r:id="rId1" xr:uid="{4C4DB9CF-C79C-4E5A-A850-965613BF762B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="v">
+      <legacyDrawing r:id="rId3"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -6783,14 +7790,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2" t="s">
         <v>1</v>
@@ -6803,19 +7810,19 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70" t="s">
+      <c r="F2" s="67"/>
+      <c r="G2" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -6834,10 +7841,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="71"/>
+      <c r="H3" s="68"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -6855,10 +7862,10 @@
         <v>14</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="68"/>
+      <c r="H4" s="65"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -6880,25 +7887,25 @@
       <c r="F5" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="66" t="s">
+      <c r="G5" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="66"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="82" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="86" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="82"/>
+      <c r="H6" s="86"/>
       <c r="I6" s="55" t="s">
         <v>74</v>
       </c>
@@ -6907,328 +7914,328 @@
       <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
+      <c r="B11" s="75"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
+      <c r="B12" s="75"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="75"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="59"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="78" t="s">
+      <c r="B16" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="67" t="s">
+      <c r="A17" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67" t="s">
+      <c r="C17" s="70"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67" t="s">
+      <c r="F17" s="70"/>
+      <c r="G17" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="67"/>
-      <c r="I17" s="67" t="s">
+      <c r="H17" s="70"/>
+      <c r="I17" s="70" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="67"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
+      <c r="A18" s="70"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
       <c r="G18" s="18" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="67"/>
+      <c r="I18" s="70"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44">
         <v>1</v>
       </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
+      <c r="B19" s="84"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="44"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
+      <c r="B21" s="84"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="84"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="44"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="44"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="44"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="72"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="84"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="84"/>
+      <c r="F23" s="84"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="44"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
+      <c r="B24" s="84"/>
+      <c r="C24" s="84"/>
+      <c r="D24" s="84"/>
+      <c r="E24" s="84"/>
+      <c r="F24" s="84"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="72"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
+      <c r="B25" s="84"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="84"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="72"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="72"/>
+      <c r="B27" s="84"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
+      <c r="B28" s="84"/>
+      <c r="C28" s="84"/>
+      <c r="D28" s="84"/>
+      <c r="E28" s="84"/>
+      <c r="F28" s="84"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
+      <c r="B29" s="84"/>
+      <c r="C29" s="84"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
-      <c r="B30" s="72"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="84"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
-      <c r="B31" s="72"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="84"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
-      <c r="B33" s="72"/>
-      <c r="C33" s="72"/>
-      <c r="D33" s="72"/>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
+      <c r="B33" s="84"/>
+      <c r="C33" s="84"/>
+      <c r="D33" s="84"/>
+      <c r="E33" s="84"/>
+      <c r="F33" s="84"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="44"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="44"/>
-      <c r="B34" s="72"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
+      <c r="B34" s="84"/>
+      <c r="C34" s="84"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="84"/>
+      <c r="F34" s="84"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="44"/>
@@ -7259,46 +8266,46 @@
       <c r="A37" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="61"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
       <c r="E37" t="s">
         <v>83</v>
       </c>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
-      <c r="B38" s="59"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="59"/>
+      <c r="B38" s="75"/>
+      <c r="C38" s="75"/>
+      <c r="D38" s="75"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="75"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="75"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
-      <c r="B39" s="59"/>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="59"/>
-      <c r="I39" s="59"/>
+      <c r="B39" s="75"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="75"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="75"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
-      <c r="B40" s="59"/>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="59"/>
+      <c r="B40" s="75"/>
+      <c r="C40" s="75"/>
+      <c r="D40" s="75"/>
+      <c r="F40" s="75"/>
+      <c r="G40" s="75"/>
+      <c r="H40" s="75"/>
+      <c r="I40" s="75"/>
     </row>
     <row r="41" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="58" t="s">
@@ -7313,12 +8320,52 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:I18"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="B6:F6"/>
@@ -7331,52 +8378,12 @@
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:D18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>

--- a/Testing-reportHW04_6810301028.xlsx
+++ b/Testing-reportHW04_6810301028.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my-homework_backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BE5173C4-87BC-473F-B2DE-1E156ED542D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{22998204-D4E6-4060-9EEC-FBD34CF3E069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
@@ -48,106 +48,6 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Sarayut Chaisuriya</author>
-  </authors>
-  <commentList>
-    <comment ref="D19" authorId="0" shapeId="2049" xr:uid="{00000000-0006-0000-0100-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Sarayut Chaisuriya:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-require at index time</t>
-        </r>
-      </text>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="v"/>
-        <mc:Fallback>
-          <commentPr defaultSize="0" autoFill="0" autoLine="0">
-            <anchor>
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>137160</xdr:colOff>
-                <xdr:row>16</xdr:row>
-                <xdr:rowOff>129540</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1508760</xdr:colOff>
-                <xdr:row>21</xdr:row>
-                <xdr:rowOff>152400</xdr:rowOff>
-              </to>
-            </anchor>
-          </commentPr>
-        </mc:Fallback>
-      </mc:AlternateContent>
-    </comment>
-    <comment ref="D21" authorId="0" shapeId="2050" xr:uid="{00000000-0006-0000-0100-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Sarayut Chaisuriya:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-require at index time</t>
-        </r>
-      </text>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="v"/>
-        <mc:Fallback>
-          <commentPr defaultSize="0" autoFill="0" autoLine="0">
-            <anchor>
-              <from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>137160</xdr:colOff>
-                <xdr:row>18</xdr:row>
-                <xdr:rowOff>121920</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>1508760</xdr:colOff>
-                <xdr:row>23</xdr:row>
-                <xdr:rowOff>144780</xdr:rowOff>
-              </to>
-            </anchor>
-          </commentPr>
-        </mc:Fallback>
-      </mc:AlternateContent>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Sarayut Chaisuriya</author>
@@ -213,13 +113,13 @@
             <anchor>
               <from>
                 <xdr:col>8</xdr:col>
-                <xdr:colOff>2110740</xdr:colOff>
+                <xdr:colOff>1798320</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>601980</xdr:colOff>
+                <xdr:colOff>289560</xdr:colOff>
                 <xdr:row>9</xdr:row>
                 <xdr:rowOff>68580</xdr:rowOff>
               </to>
@@ -232,7 +132,7 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Sarayut Chaisuriya</author>
@@ -298,13 +198,13 @@
             <anchor>
               <from>
                 <xdr:col>13</xdr:col>
-                <xdr:colOff>472440</xdr:colOff>
+                <xdr:colOff>373380</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </from>
               <to>
-                <xdr:col>16</xdr:col>
-                <xdr:colOff>15240</xdr:colOff>
+                <xdr:col>15</xdr:col>
+                <xdr:colOff>525780</xdr:colOff>
                 <xdr:row>9</xdr:row>
                 <xdr:rowOff>68580</xdr:rowOff>
               </to>
@@ -317,7 +217,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Sarayut Chaisuriya</author>
@@ -383,13 +283,13 @@
             <anchor>
               <from>
                 <xdr:col>8</xdr:col>
-                <xdr:colOff>1409700</xdr:colOff>
+                <xdr:colOff>1303020</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>9</xdr:col>
-                <xdr:colOff>411480</xdr:colOff>
+                <xdr:colOff>304800</xdr:colOff>
                 <xdr:row>9</xdr:row>
                 <xdr:rowOff>68580</xdr:rowOff>
               </to>
@@ -402,7 +302,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Sarayut Chaisuriya</author>
@@ -468,13 +368,13 @@
             <anchor>
               <from>
                 <xdr:col>8</xdr:col>
-                <xdr:colOff>1409700</xdr:colOff>
+                <xdr:colOff>1280160</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>220980</xdr:colOff>
+                <xdr:colOff>91440</xdr:colOff>
                 <xdr:row>9</xdr:row>
                 <xdr:rowOff>68580</xdr:rowOff>
               </to>
@@ -487,7 +387,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Sarayut Chaisuriya</author>
@@ -563,13 +463,13 @@
             <anchor>
               <from>
                 <xdr:col>8</xdr:col>
-                <xdr:colOff>1135380</xdr:colOff>
+                <xdr:colOff>952500</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>45720</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>8</xdr:col>
-                <xdr:colOff>2506980</xdr:colOff>
+                <xdr:colOff>2324100</xdr:colOff>
                 <xdr:row>9</xdr:row>
                 <xdr:rowOff>68580</xdr:rowOff>
               </to>
@@ -582,7 +482,7 @@
 </comments>
 </file>
 
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Sarayut Chaisuriya</author>
@@ -677,7 +577,7 @@
 </comments>
 </file>
 
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Sarayut Chaisuriya</author>
@@ -773,14 +673,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="498" uniqueCount="164">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="496" uniqueCount="161">
   <si>
     <t>Test Report</t>
   </si>
   <si>
-    <t>http://www.thai-engine.com</t>
-  </si>
-  <si>
     <t>Product</t>
   </si>
   <si>
@@ -928,9 +825,6 @@
     <t>H/W</t>
   </si>
   <si>
-    <t>X86 pc</t>
-  </si>
-  <si>
     <t>OS</t>
   </si>
   <si>
@@ -950,9 +844,6 @@
   </si>
   <si>
     <t>Indexer</t>
-  </si>
-  <si>
-    <t>same machine with searcher</t>
   </si>
   <si>
     <t>Article Data</t>
@@ -1739,53 +1630,59 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1793,67 +1690,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1926,23 +1817,23 @@
     <mc:Fallback>
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>137160</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>129540</xdr:rowOff>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>1798320</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>45720</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>1508760</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>289560</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>68580</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2049" name="Comment 1" hidden="1">
+            <xdr:cNvPr id="3073" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F3F2C61-ECD0-4E17-AF1B-C444BB85868F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D41C8FF4-82BA-4ED4-8139-B4BFD1105852}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1952,7 +1843,7 @@
           </xdr:nvSpPr>
           <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="4015740" y="2933700"/>
+              <a:off x="9502140" y="967740"/>
               <a:ext cx="1371600" cy="861060"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2025,105 +1916,8 @@
                   <a:ea typeface="Tahoma"/>
                   <a:cs typeface="Tahoma"/>
                 </a:rPr>
-                <a:t>require at index time</a:t>
+                <a:t>-Search Command</a:t>
               </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:v="urn:schemas-microsoft-com:vml" Requires="v"/>
-    <mc:Fallback>
-      <xdr:twoCellAnchor editAs="absolute">
-        <xdr:from>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>137160</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>121920</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>4</xdr:col>
-          <xdr:colOff>1508760</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>144780</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2050" name="Comment 2" hidden="1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03E9A2EB-D779-4A66-AB99-10DF4950054B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1">
-              <a:spLocks noChangeArrowheads="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="4015740" y="3261360"/>
-              <a:ext cx="1371600" cy="861060"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFE1" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="80"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="510000"/>
-              </a:solidFill>
-              <a:miter lim="800%"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="510000"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-              <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-                <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="1"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="0" bIns="0" anchor="t" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0%">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma"/>
-                  <a:ea typeface="Tahoma"/>
-                  <a:cs typeface="Tahoma"/>
-                </a:rPr>
-                <a:t>Sarayut Chaisuriya:</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Tahoma"/>
-                <a:ea typeface="Tahoma"/>
-                <a:cs typeface="Tahoma"/>
-              </a:endParaRPr>
             </a:p>
             <a:p>
               <a:pPr algn="l" rtl="0">
@@ -2138,7 +1932,39 @@
                   <a:ea typeface="Tahoma"/>
                   <a:cs typeface="Tahoma"/>
                 </a:rPr>
-                <a:t>require at index time</a:t>
+                <a:t>-Stability test</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma"/>
+                  <a:ea typeface="Tahoma"/>
+                  <a:cs typeface="Tahoma"/>
+                </a:rPr>
+                <a:t>-Performance Test</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Tahoma"/>
+                  <a:ea typeface="Tahoma"/>
+                  <a:cs typeface="Tahoma"/>
+                </a:rPr>
+                <a:t>-Generic</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -2152,28 +1978,67 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="0" cy="247646"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="logo3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC919275-1FA8-427D-8198-843FB7E0FBD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8134350" y="0"/>
+          <a:ext cx="0" cy="247646"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:v="urn:schemas-microsoft-com:vml" Requires="v"/>
     <mc:Fallback>
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>2110740</xdr:colOff>
+          <xdr:col>13</xdr:col>
+          <xdr:colOff>373380</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>45720</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>601980</xdr:colOff>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>525780</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>68580</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3073" name="Comment 1" hidden="1">
+            <xdr:cNvPr id="4097" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59C4C62B-FBDE-40EA-A416-DF548F6E7238}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D95CB86-BD0D-4BB1-BED2-AD3DD3E6BB65}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2183,7 +2048,7 @@
           </xdr:nvSpPr>
           <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="9502140" y="967740"/>
+              <a:off x="13357860" y="967740"/>
               <a:ext cx="1371600" cy="861060"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2331,7 +2196,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="logo3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC919275-1FA8-427D-8198-843FB7E0FBD2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18487714-2030-4B90-9B46-8E489AE4DCE6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2362,23 +2227,23 @@
     <mc:Fallback>
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
-          <xdr:col>13</xdr:col>
-          <xdr:colOff>472440</xdr:colOff>
+          <xdr:col>8</xdr:col>
+          <xdr:colOff>1303020</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>45720</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>16</xdr:col>
-          <xdr:colOff>15240</xdr:colOff>
+          <xdr:col>9</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>68580</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4097" name="Comment 1" hidden="1">
+            <xdr:cNvPr id="5121" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68644429-539A-42C5-9748-0E7E1B184C6D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF7FBE58-73CA-4D9A-9ED8-000CF304C145}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2388,7 +2253,7 @@
           </xdr:nvSpPr>
           <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="13357860" y="967740"/>
+              <a:off x="9502140" y="967740"/>
               <a:ext cx="1371600" cy="861060"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2525,7 +2390,7 @@
 <xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>742950</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2536,7 +2401,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="logo3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18487714-2030-4B90-9B46-8E489AE4DCE6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8886AB46-C0EC-47A4-9754-39E7BEF43CA4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2568,22 +2433,22 @@
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>1409700</xdr:colOff>
+          <xdr:colOff>1280160</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>45720</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>411480</xdr:colOff>
+          <xdr:col>10</xdr:col>
+          <xdr:colOff>91440</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>68580</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5121" name="Comment 1" hidden="1">
+            <xdr:cNvPr id="6145" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8406CD3A-79C2-4925-B836-6ECE4CC18A39}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75FBC91B-D4CF-4368-8882-BD6E798C74CD}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2741,211 +2606,6 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="logo3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8886AB46-C0EC-47A4-9754-39E7BEF43CA4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8134350" y="0"/>
-          <a:ext cx="0" cy="247646"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:v="urn:schemas-microsoft-com:vml" Requires="v"/>
-    <mc:Fallback>
-      <xdr:twoCellAnchor editAs="absolute">
-        <xdr:from>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>1409700</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>45720</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>220980</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>68580</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="6145" name="Comment 1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DAAD8E7-BACB-45FA-8038-971CEB95F1BA}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1">
-              <a:spLocks noChangeArrowheads="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="9502140" y="967740"/>
-              <a:ext cx="1371600" cy="861060"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="FFFFE1" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="80"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="510000"/>
-              </a:solidFill>
-              <a:miter lim="800%"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="510000"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-              <a:ext uri="{53640926-AAD7-44D8-BBD7-CCE9431645EC}">
-                <a14:shadowObscured xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="1"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="0" bIns="0" anchor="t" upright="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0%">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma"/>
-                  <a:ea typeface="Tahoma"/>
-                  <a:cs typeface="Tahoma"/>
-                </a:rPr>
-                <a:t>Sarayut Chaisuriya:</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Tahoma"/>
-                <a:ea typeface="Tahoma"/>
-                <a:cs typeface="Tahoma"/>
-              </a:endParaRPr>
-            </a:p>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma"/>
-                  <a:ea typeface="Tahoma"/>
-                  <a:cs typeface="Tahoma"/>
-                </a:rPr>
-                <a:t>-Search Command</a:t>
-              </a:r>
-            </a:p>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma"/>
-                  <a:ea typeface="Tahoma"/>
-                  <a:cs typeface="Tahoma"/>
-                </a:rPr>
-                <a:t>-Stability test</a:t>
-              </a:r>
-            </a:p>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma"/>
-                  <a:ea typeface="Tahoma"/>
-                  <a:cs typeface="Tahoma"/>
-                </a:rPr>
-                <a:t>-Performance Test</a:t>
-              </a:r>
-            </a:p>
-            <a:p>
-              <a:pPr algn="l" rtl="0">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0%">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Tahoma"/>
-                  <a:ea typeface="Tahoma"/>
-                  <a:cs typeface="Tahoma"/>
-                </a:rPr>
-                <a:t>-Generic</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Fallback>
-  </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="0" cy="247646"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="logo3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D751A23-8693-4DF1-911E-C66B2195167D}"/>
             </a:ext>
           </a:extLst>
@@ -2978,13 +2638,13 @@
       <xdr:twoCellAnchor editAs="absolute">
         <xdr:from>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>1135380</xdr:colOff>
+          <xdr:colOff>952500</xdr:colOff>
           <xdr:row>4</xdr:row>
           <xdr:rowOff>45720</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>2506980</xdr:colOff>
+          <xdr:colOff>2324100</xdr:colOff>
           <xdr:row>9</xdr:row>
           <xdr:rowOff>68580</xdr:rowOff>
         </xdr:to>
@@ -2993,7 +2653,7 @@
             <xdr:cNvPr id="7169" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA293F45-59F9-4716-B428-68A8802878B4}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9327DBE-9B06-4470-AE3B-BADF7190185F}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3152,7 +2812,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:v="urn:schemas-microsoft-com:vml" Requires="v"/>
@@ -3175,7 +2835,7 @@
             <xdr:cNvPr id="8193" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E8548E1-D20A-433D-958C-856CE7D08280}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{525856F1-91B5-478A-8F94-876E949ED2C4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3334,47 +2994,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1085850" cy="247646"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="logo3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBADCFBA-1C03-4F06-A4B0-DBE77A9B15C7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8134350" y="0"/>
-          <a:ext cx="1085850" cy="247646"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:v="urn:schemas-microsoft-com:vml" Requires="v"/>
     <mc:Fallback>
@@ -3396,7 +3017,7 @@
             <xdr:cNvPr id="9217" name="Comment 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{962B9768-6B49-499B-A637-567CC8DC14DA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12CD466A-510C-4EF9-9285-6BB02F31FC13}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3868,172 +3489,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="1"/>
       <c r="J1" s="65" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="77" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="68"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="77" t="s">
+      <c r="G2" s="68"/>
+      <c r="H2" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="7" t="d">
         <v>2026-06-30</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="78"/>
+      <c r="I3" s="69"/>
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="75" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="75"/>
+      <c r="I4" s="66"/>
       <c r="J4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>17</v>
-      </c>
       <c r="C5" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="H5" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="73" t="s">
+      <c r="I5" s="70"/>
+      <c r="J5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="73"/>
-      <c r="J5" s="14" t="s">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="71" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="74" t="s">
+      <c r="B6" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="74" t="s">
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74" t="s">
+      <c r="F6" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="74" t="s">
+      <c r="G6" s="71"/>
+      <c r="H6" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74" t="s">
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="71"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="74"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="17" t="s">
+      <c r="G7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="H7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="I7" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="J7" s="18" t="s">
         <v>30</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="69" t="str">
+        <v>31</v>
+      </c>
+      <c r="B8" s="72" t="str">
         <f>'TC01'!B6</f>
         <v>Load_Data_Range_CSV</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
       <c r="E8" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="20"/>
@@ -4043,16 +3664,16 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="70" t="str">
+        <v>33</v>
+      </c>
+      <c r="B9" s="73" t="str">
         <f>'TC02'!B6</f>
         <v>Invalid_Range_Validation</v>
       </c>
-      <c r="C9" s="70"/>
-      <c r="D9" s="70"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
       <c r="E9" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="5"/>
@@ -4062,16 +3683,16 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="70" t="str">
+        <v>34</v>
+      </c>
+      <c r="B10" s="73" t="str">
         <f>'TC03'!B6</f>
         <v>Data_Filtering_Exe</v>
       </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
       <c r="E10" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="5"/>
@@ -4081,16 +3702,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="70" t="str">
+        <v>35</v>
+      </c>
+      <c r="B11" s="73" t="str">
         <f>'TC04'!B6</f>
         <v>Read_As_Text_UI_Test</v>
       </c>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
       <c r="E11" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11" s="24"/>
       <c r="G11" s="5"/>
@@ -4100,15 +3721,15 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
+        <v>36</v>
+      </c>
+      <c r="B12" s="75" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
       <c r="E12" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="24"/>
       <c r="G12" s="5"/>
@@ -4118,15 +3739,15 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="B13" s="72" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
+        <v>146</v>
+      </c>
+      <c r="B13" s="75" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
       <c r="E13" s="28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13" s="24"/>
       <c r="G13" s="5"/>
@@ -4136,9 +3757,9 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="28"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
       <c r="E14" s="28"/>
       <c r="F14" s="24"/>
       <c r="G14" s="5"/>
@@ -4148,9 +3769,9 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
-      <c r="B15" s="72"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
       <c r="E15" s="28"/>
       <c r="F15" s="24"/>
       <c r="G15" s="5"/>
@@ -4160,9 +3781,9 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
-      <c r="B16" s="72"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
+      <c r="B16" s="75"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
       <c r="E16" s="28"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -4172,9 +3793,9 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
-      <c r="B17" s="72"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
       <c r="E17" s="28"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -4184,9 +3805,9 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="28"/>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
       <c r="E18" s="28"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -4196,9 +3817,9 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="28"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
       <c r="E19" s="28"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -4208,9 +3829,9 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="28"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
       <c r="E20" s="28"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -4220,9 +3841,9 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
-      <c r="B21" s="71"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="71"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74"/>
       <c r="E21" s="29"/>
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
@@ -4232,14 +3853,14 @@
     </row>
     <row r="22" spans="1:10" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="67" t="s">
+      <c r="C22" s="77"/>
+      <c r="G22" s="34" t="s">
         <v>39</v>
-      </c>
-      <c r="C22" s="67"/>
-      <c r="G22" s="34" t="s">
-        <v>40</v>
       </c>
       <c r="H22" s="35">
         <f>COUNTA(H8:H21)</f>
@@ -4252,91 +3873,87 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="68"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="68"/>
+        <v>30</v>
+      </c>
+      <c r="B23" s="78"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="78"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="66"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="76"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="66"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="66"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="76"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="66"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="66"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="76"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="66"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="66"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="76"/>
     </row>
     <row r="28" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="76"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
+      <c r="F28" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="66"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="66"/>
-      <c r="F28" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B25:J25"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:D10"/>
@@ -4351,14 +3968,18 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B25:J25"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -4371,7 +3992,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4384,23 +4005,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="A1" s="83" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
+      <c r="A1" s="80" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="84" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="84"/>
+        <v>1</v>
+      </c>
+      <c r="B2" s="81" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="81"/>
       <c r="D2" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E2" s="39" t="d">
         <v>2026-06-30</v>
@@ -4408,89 +4029,87 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
+        <v>6</v>
+      </c>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
       <c r="D3" s="34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="36">
-        <v>1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="70" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="70"/>
+        <v>11</v>
+      </c>
+      <c r="B4" s="73" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="73"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="C5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>48</v>
-      </c>
       <c r="E5" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="82" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="82"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
       <c r="E6" s="42"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="43"/>
       <c r="B7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="82" t="s">
-        <v>144</v>
-      </c>
-      <c r="D7" s="82"/>
+        <v>50</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="79"/>
       <c r="E7" s="42"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="43"/>
       <c r="B8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
+        <v>51</v>
+      </c>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
       <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="43"/>
       <c r="B9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
+        <v>52</v>
+      </c>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
       <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="43"/>
       <c r="B10" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10" s="44"/>
       <c r="D10" s="44"/>
@@ -4499,7 +4118,7 @@
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="43"/>
       <c r="B11" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" s="44"/>
       <c r="D11" s="44"/>
@@ -4508,7 +4127,7 @@
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="43"/>
       <c r="B12" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" s="44"/>
       <c r="D12" s="44"/>
@@ -4517,62 +4136,60 @@
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="43"/>
       <c r="B13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
+        <v>30</v>
+      </c>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
       <c r="E13" s="42"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="43"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="81"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
       <c r="E14" s="42"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="82" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="82"/>
+        <v>49</v>
+      </c>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
       <c r="E15" s="42"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="43"/>
       <c r="B16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81"/>
+        <v>50</v>
+      </c>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
       <c r="E16" s="42"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="43"/>
       <c r="B17" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="81"/>
-      <c r="D17" s="81"/>
+        <v>51</v>
+      </c>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
       <c r="E17" s="42"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="43"/>
       <c r="B18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
+        <v>52</v>
+      </c>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
       <c r="E18" s="42"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="43"/>
       <c r="B19" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C19" s="44"/>
       <c r="D19" s="44"/>
@@ -4581,7 +4198,7 @@
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="43"/>
       <c r="B20" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" s="44"/>
       <c r="D20" s="44"/>
@@ -4590,7 +4207,7 @@
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="43"/>
       <c r="B21" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -4599,59 +4216,59 @@
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="45"/>
       <c r="B22" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="81"/>
-      <c r="D22" s="81"/>
+        <v>30</v>
+      </c>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
       <c r="E22" s="42"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="74" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="74"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
+      <c r="A24" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="47"/>
       <c r="B25" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="80" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="80"/>
+        <v>58</v>
+      </c>
+      <c r="C25" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="83"/>
       <c r="E25" s="48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="72" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="72"/>
+        <v>60</v>
+      </c>
+      <c r="C26" s="75" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="75"/>
       <c r="E26" s="42"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="49"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
       <c r="E27" s="42"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="49"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
       <c r="E28" s="42"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -4662,119 +4279,130 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="49"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
+      <c r="C30" s="75"/>
+      <c r="D30" s="75"/>
       <c r="E30" s="42"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="72"/>
-      <c r="D31" s="72"/>
+        <v>61</v>
+      </c>
+      <c r="C31" s="75"/>
+      <c r="D31" s="75"/>
       <c r="E31" s="42"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="49"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="75"/>
       <c r="E32" s="42"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="49"/>
-      <c r="C33" s="72"/>
-      <c r="D33" s="72"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="75"/>
       <c r="E33" s="42"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="49"/>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
       <c r="E34" s="42"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="74"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
+      <c r="A35" s="71" t="s">
+        <v>62</v>
+      </c>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="49"/>
       <c r="B36" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="80" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" s="80"/>
+        <v>63</v>
+      </c>
+      <c r="C36" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="83"/>
       <c r="E36" s="48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="49" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B37" s="42"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="79"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="85"/>
       <c r="E37" s="42"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="49"/>
       <c r="B38" s="42"/>
-      <c r="C38" s="79"/>
-      <c r="D38" s="79"/>
+      <c r="C38" s="85"/>
+      <c r="D38" s="85"/>
       <c r="E38" s="42"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="49"/>
       <c r="B39" s="42"/>
-      <c r="C39" s="79"/>
-      <c r="D39" s="79"/>
+      <c r="C39" s="85"/>
+      <c r="D39" s="85"/>
       <c r="E39" s="42"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="49"/>
       <c r="B40" s="42"/>
-      <c r="C40" s="79"/>
-      <c r="D40" s="79"/>
+      <c r="C40" s="85"/>
+      <c r="D40" s="85"/>
       <c r="E40" s="42"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="49" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B41" s="42"/>
-      <c r="C41" s="79"/>
-      <c r="D41" s="79"/>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85"/>
       <c r="E41" s="42"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="49"/>
       <c r="B42" s="42"/>
-      <c r="C42" s="79"/>
-      <c r="D42" s="79"/>
+      <c r="C42" s="85"/>
+      <c r="D42" s="85"/>
       <c r="E42" s="42"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="51"/>
       <c r="B43" s="42"/>
-      <c r="C43" s="79"/>
-      <c r="D43" s="79"/>
+      <c r="C43" s="85"/>
+      <c r="D43" s="85"/>
       <c r="E43" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
@@ -4787,33 +4415,16 @@
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.75000000000000011" right="0.75000000000000011" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId1"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="v">
-      <legacyDrawing r:id="rId2"/>
-    </mc:Choice>
-  </mc:AlternateContent>
 </worksheet>
 </file>
 
@@ -4826,7 +4437,7 @@
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
     <col min="3" max="3" width="9.5546875" customWidth="1"/>
     <col min="4" max="4" width="22.21875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" customWidth="1"/>
     <col min="6" max="6" width="20.77734375" customWidth="1"/>
     <col min="7" max="8" width="5.21875" customWidth="1"/>
     <col min="9" max="9" width="33.109375" customWidth="1"/>
@@ -4834,245 +4445,245 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="88" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+        <v>140</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="7" t="d">
         <v>2026-06-30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="78"/>
+      <c r="G3" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="69"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="75"/>
+      <c r="G4" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="66"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="73"/>
+      <c r="G5" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="70"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="89" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="89"/>
+        <v>22</v>
+      </c>
+      <c r="B6" s="82" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="87"/>
       <c r="I6" s="55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="84" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
+        <v>72</v>
+      </c>
+      <c r="B7" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="66" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
+        <v>73</v>
+      </c>
+      <c r="B9" s="76" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74" t="s">
-        <v>31</v>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="74"/>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
+      <c r="A13" s="71"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
       <c r="G13" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="74"/>
+      <c r="I13" s="71"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="44">
         <v>1</v>
       </c>
-      <c r="B14" s="86" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="86"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="86" t="s">
-        <v>95</v>
-      </c>
-      <c r="F14" s="86"/>
+      <c r="B14" s="88" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="88" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="88"/>
       <c r="G14" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="44"/>
@@ -5081,17 +4692,17 @@
       <c r="A15" s="44">
         <v>2</v>
       </c>
-      <c r="B15" s="86" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86" t="s">
-        <v>97</v>
-      </c>
-      <c r="F15" s="86"/>
+      <c r="B15" s="88" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="88"/>
       <c r="G15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="44"/>
@@ -5100,17 +4711,17 @@
       <c r="A16" s="44">
         <v>3</v>
       </c>
-      <c r="B16" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="86"/>
+      <c r="B16" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="88"/>
       <c r="G16" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="44"/>
@@ -5119,46 +4730,46 @@
       <c r="A17" s="44">
         <v>4</v>
       </c>
-      <c r="B17" s="86" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86" t="s">
-        <v>101</v>
-      </c>
-      <c r="F17" s="86"/>
+      <c r="B17" s="88" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="88"/>
       <c r="G17" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="44"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="87"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F20" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G20" s="56">
         <f>COUNTA(G14:G19)</f>
@@ -5171,44 +4782,44 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="57" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
+        <v>79</v>
+      </c>
+      <c r="B22" s="78"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="78"/>
       <c r="E22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
+        <v>80</v>
+      </c>
+      <c r="F22" s="78"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="78"/>
+      <c r="I22" s="78"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -5216,6 +4827,29 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:I13"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -5228,29 +4862,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.19000000000000003" top="0.27" bottom="0.16000000000000003" header="0.27" footer="0.16000000000000003"/>
   <pageSetup paperSize="0" scale="90" fitToWidth="0" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -5273,7 +4884,7 @@
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
     <col min="3" max="3" width="9.5546875" customWidth="1"/>
     <col min="4" max="4" width="22.21875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="32.44140625" customWidth="1"/>
     <col min="7" max="8" width="5.21875" customWidth="1"/>
     <col min="9" max="9" width="32.88671875" customWidth="1"/>
@@ -5281,255 +4892,255 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="88" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
       <c r="H1" s="1"/>
       <c r="I1" s="65" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="102" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="103"/>
-      <c r="E2" s="102" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="103"/>
-      <c r="G2" s="102" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="104"/>
-      <c r="I2" s="103"/>
+        <v>140</v>
+      </c>
+      <c r="C2" s="90" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="91"/>
+      <c r="E2" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="91"/>
+      <c r="G2" s="90" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="92"/>
+      <c r="I2" s="91"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="7" t="d">
         <v>2026-06-30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="105"/>
+      <c r="G3" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="93"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="106"/>
+      <c r="G4" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="94"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="107"/>
+      <c r="G5" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="95"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="108" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="108"/>
+        <v>22</v>
+      </c>
+      <c r="B6" s="82" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="96" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="96"/>
       <c r="I6" s="55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
+        <v>72</v>
+      </c>
+      <c r="B7" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="85" t="s">
-        <v>114</v>
-      </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
+        <v>73</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="97" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="99" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="100"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="99" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="66" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="92" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="94" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="95"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="94" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="96"/>
-      <c r="G13" s="100" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="101"/>
-      <c r="I13" s="92" t="s">
-        <v>31</v>
+      <c r="F13" s="101"/>
+      <c r="G13" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="106"/>
+      <c r="I13" s="97" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="93"/>
-      <c r="B14" s="97"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="97"/>
-      <c r="F14" s="99"/>
+      <c r="A14" s="98"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="104"/>
       <c r="G14" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="93"/>
+      <c r="I14" s="98"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
-      <c r="B15" s="90" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15" s="85"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="90" t="s">
-        <v>106</v>
-      </c>
-      <c r="F15" s="82"/>
+      <c r="B15" s="107" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="82"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="107" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="79"/>
       <c r="G15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="44"/>
@@ -5538,17 +5149,17 @@
       <c r="A16" s="44">
         <v>2</v>
       </c>
-      <c r="B16" s="90" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="85"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="90" t="s">
-        <v>147</v>
-      </c>
-      <c r="F16" s="82"/>
+      <c r="B16" s="107" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="82"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="107" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" s="79"/>
       <c r="G16" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="44"/>
@@ -5557,17 +5168,17 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="90" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="90"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="90" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" s="90"/>
+      <c r="B17" s="107" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="107" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="107"/>
       <c r="G17" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="44"/>
@@ -5576,35 +5187,35 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="90" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="90" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="82"/>
+      <c r="B18" s="107" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="82"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="107" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="79"/>
       <c r="G18" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="81"/>
+      <c r="B19" s="108"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="84"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F20" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G20" s="56">
         <f>COUNTA(G15:G19)</f>
@@ -5617,64 +5228,64 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="57" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
+        <v>79</v>
+      </c>
+      <c r="B22" s="78"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="78"/>
       <c r="E22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
+        <v>80</v>
+      </c>
+      <c r="F22" s="78"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="78"/>
+      <c r="I22" s="78"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="66"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="66"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="66"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -5682,6 +5293,30 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="B9:I9"/>
@@ -5696,30 +5331,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -5744,7 +5355,7 @@
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
     <col min="3" max="3" width="9.5546875" customWidth="1"/>
     <col min="4" max="4" width="22.21875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
     <col min="6" max="6" width="31" customWidth="1"/>
     <col min="7" max="8" width="5.21875" customWidth="1"/>
     <col min="9" max="9" width="34.5546875" customWidth="1"/>
@@ -5752,255 +5363,255 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="88" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
       <c r="H1" s="1"/>
       <c r="I1" s="65" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+        <v>140</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="7" t="d">
         <v>2026-06-30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="78"/>
+      <c r="G3" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="69"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="75"/>
+      <c r="G4" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="66"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="73"/>
+      <c r="G5" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="70"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="89" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="89"/>
+        <v>22</v>
+      </c>
+      <c r="B6" s="82" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="87" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="87"/>
       <c r="I6" s="55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="85" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
+        <v>72</v>
+      </c>
+      <c r="B7" s="82" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="85" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
+        <v>73</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="85" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74" t="s">
-        <v>31</v>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="74"/>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
       <c r="G14" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="74"/>
+      <c r="I14" s="71"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
       <c r="B15" s="109" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C15" s="109"/>
       <c r="D15" s="109"/>
       <c r="E15" s="109" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F15" s="109"/>
       <c r="G15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="44"/>
@@ -6010,16 +5621,16 @@
         <v>2</v>
       </c>
       <c r="B16" s="109" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C16" s="109"/>
       <c r="D16" s="109"/>
       <c r="E16" s="109" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F16" s="109"/>
       <c r="G16" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="44"/>
@@ -6029,16 +5640,16 @@
         <v>3</v>
       </c>
       <c r="B17" s="109" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C17" s="109"/>
       <c r="D17" s="109"/>
       <c r="E17" s="109" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F17" s="109"/>
       <c r="G17" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="44"/>
@@ -6048,23 +5659,23 @@
         <v>4</v>
       </c>
       <c r="B18" s="109" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C18" s="109"/>
       <c r="D18" s="109"/>
       <c r="E18" s="109" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F18" s="109"/>
       <c r="G18" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" s="56">
         <f>COUNTA(G15:G18)</f>
@@ -6077,64 +5688,64 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="57" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68"/>
+        <v>79</v>
+      </c>
+      <c r="B21" s="78"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="78"/>
       <c r="E21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
+        <v>80</v>
+      </c>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="66"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76"/>
     </row>
     <row r="25" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E25" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -6142,6 +5753,30 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -6154,30 +5789,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -6201,7 +5812,7 @@
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
     <col min="3" max="3" width="9.5546875" customWidth="1"/>
     <col min="4" max="4" width="22.21875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" customWidth="1"/>
     <col min="6" max="6" width="31" customWidth="1"/>
     <col min="7" max="8" width="5.21875" customWidth="1"/>
     <col min="9" max="9" width="28.44140625" customWidth="1"/>
@@ -6209,257 +5820,257 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="88" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="C2" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="D3" s="7" t="d">
         <v>2026-06-30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="78"/>
+      <c r="G3" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="69"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="10">
-        <v>2</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>14</v>
-      </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="75"/>
+      <c r="G4" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="66"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="73"/>
+      <c r="G5" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="70"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="89" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="89"/>
+        <v>22</v>
+      </c>
+      <c r="B6" s="82" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="87" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="87"/>
       <c r="I6" s="55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="85" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
+        <v>72</v>
+      </c>
+      <c r="B7" s="82" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="85" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
+        <v>73</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="85" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74" t="s">
-        <v>31</v>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="74"/>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
       <c r="G14" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="74"/>
+      <c r="I14" s="71"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
       <c r="B15" s="109" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C15" s="109"/>
       <c r="D15" s="109"/>
       <c r="E15" s="109" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F15" s="109"/>
       <c r="G15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="44"/>
@@ -6469,16 +6080,16 @@
         <v>2</v>
       </c>
       <c r="B16" s="109" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C16" s="109"/>
       <c r="D16" s="109"/>
       <c r="E16" s="109" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F16" s="109"/>
       <c r="G16" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="44"/>
@@ -6487,46 +6098,46 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="79" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79" t="s">
-        <v>120</v>
-      </c>
-      <c r="F17" s="79"/>
+      <c r="B17" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="85"/>
       <c r="G17" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="44"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F20" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G20" s="56">
         <f>COUNTA(G15:G19)</f>
@@ -6539,64 +6150,64 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="57" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
+        <v>79</v>
+      </c>
+      <c r="B22" s="78"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="78"/>
       <c r="E22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
+        <v>80</v>
+      </c>
+      <c r="F22" s="78"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="78"/>
+      <c r="I22" s="78"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="66"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="66"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="66"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -6604,6 +6215,32 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="C2:D2"/>
@@ -6616,32 +6253,6 @@
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="F23:I23"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -6666,7 +6277,7 @@
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
     <col min="3" max="3" width="9.5546875" customWidth="1"/>
     <col min="4" max="4" width="22.21875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
     <col min="7" max="8" width="5.21875" customWidth="1"/>
     <col min="9" max="9" width="37.109375" customWidth="1"/>
@@ -6674,255 +6285,255 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="88" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+        <v>140</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="7" t="d">
         <v>2026-06-30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="78"/>
+      <c r="G3" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="69"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="75"/>
+      <c r="G4" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="66"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="73"/>
+      <c r="G5" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="70"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="89" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="89"/>
+        <v>22</v>
+      </c>
+      <c r="B6" s="82" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="87" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="87"/>
       <c r="I6" s="55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="85" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
+        <v>72</v>
+      </c>
+      <c r="B7" s="82" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="85" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
+        <v>73</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="85" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74" t="s">
-        <v>31</v>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="74"/>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
       <c r="G14" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="74"/>
+      <c r="I14" s="71"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="44">
         <v>1</v>
       </c>
       <c r="B15" s="109" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C15" s="109"/>
       <c r="D15" s="109"/>
       <c r="E15" s="109" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F15" s="109"/>
       <c r="G15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="44"/>
@@ -6932,16 +6543,16 @@
         <v>2</v>
       </c>
       <c r="B16" s="109" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C16" s="109"/>
       <c r="D16" s="109"/>
       <c r="E16" s="109" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F16" s="109"/>
       <c r="G16" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="44"/>
@@ -6950,17 +6561,17 @@
       <c r="A17" s="44">
         <v>3</v>
       </c>
-      <c r="B17" s="79" t="s">
-        <v>139</v>
-      </c>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79" t="s">
-        <v>140</v>
-      </c>
-      <c r="F17" s="79"/>
+      <c r="B17" s="85" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="85"/>
       <c r="G17" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="44"/>
@@ -6969,35 +6580,35 @@
       <c r="A18" s="44">
         <v>4</v>
       </c>
-      <c r="B18" s="79" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="F18" s="79"/>
+      <c r="B18" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" s="85"/>
       <c r="G18" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="44"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F20" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G20" s="56">
         <f>COUNTA(G15:G19)</f>
@@ -7010,64 +6621,64 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="57" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
+        <v>79</v>
+      </c>
+      <c r="B22" s="78"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="78"/>
       <c r="E22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
+        <v>80</v>
+      </c>
+      <c r="F22" s="78"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="78"/>
+      <c r="I22" s="78"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="66"/>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="66"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="66"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -7075,32 +6686,6 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="B24:D24"/>
@@ -7113,6 +6698,32 @@
     <mergeCell ref="F22:I22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:D14"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
@@ -7144,299 +6755,299 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="88" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
       <c r="H1" s="1"/>
       <c r="J1" s="65" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="C2" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="C3" s="63" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>9</v>
       </c>
       <c r="D3" s="7" t="d">
         <v>2026-06-30</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="78"/>
+      <c r="G3" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="69"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="60" t="s">
+      <c r="C4" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="10">
+        <v>2.1</v>
+      </c>
+      <c r="E4" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="10">
-        <v>2</v>
-      </c>
-      <c r="E4" s="62" t="s">
-        <v>14</v>
-      </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="75"/>
+      <c r="G4" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="66"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="64" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E5" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="73"/>
+      <c r="G5" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="70"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="64" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="66" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="89" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="89"/>
+        <v>22</v>
+      </c>
+      <c r="B6" s="76" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="87" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="87"/>
       <c r="I6" s="55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="64" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="66" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
+        <v>72</v>
+      </c>
+      <c r="B7" s="76" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="66" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
+        <v>73</v>
+      </c>
+      <c r="B9" s="76" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="64"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="64"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="64"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="64"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="64"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="76"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="82" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="85" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="85"/>
-      <c r="I16" s="85"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74" t="s">
-        <v>31</v>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="74"/>
-      <c r="B18" s="74"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
       <c r="G18" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="74"/>
+      <c r="I18" s="71"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>1</v>
       </c>
-      <c r="B19" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79" t="s">
-        <v>154</v>
-      </c>
-      <c r="F19" s="79"/>
+      <c r="B19" s="85" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85" t="s">
+        <v>151</v>
+      </c>
+      <c r="F19" s="85"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
@@ -7445,28 +7056,28 @@
       <c r="A20" s="4">
         <v>2</v>
       </c>
-      <c r="B20" s="79" t="s">
-        <v>155</v>
-      </c>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79" t="s">
-        <v>156</v>
-      </c>
-      <c r="F20" s="79"/>
+      <c r="B20" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="85"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85" t="s">
+        <v>153</v>
+      </c>
+      <c r="F20" s="85"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79" t="s">
-        <v>157</v>
-      </c>
-      <c r="F21" s="79"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85" t="s">
+        <v>154</v>
+      </c>
+      <c r="F21" s="85"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="44"/>
@@ -7475,15 +7086,15 @@
       <c r="A22" s="4">
         <v>3</v>
       </c>
-      <c r="B22" s="79" t="s">
-        <v>158</v>
-      </c>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79" t="s">
-        <v>159</v>
-      </c>
-      <c r="F22" s="79"/>
+      <c r="B22" s="85" t="s">
+        <v>155</v>
+      </c>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85" t="s">
+        <v>156</v>
+      </c>
+      <c r="F22" s="85"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="44"/>
@@ -7492,15 +7103,15 @@
       <c r="A23" s="4">
         <v>4</v>
       </c>
-      <c r="B23" s="79" t="s">
-        <v>160</v>
-      </c>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79" t="s">
-        <v>161</v>
-      </c>
-      <c r="F23" s="79"/>
+      <c r="B23" s="85" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="85"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85" t="s">
+        <v>158</v>
+      </c>
+      <c r="F23" s="85"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="44"/>
@@ -7509,121 +7120,121 @@
       <c r="A24" s="4">
         <v>5</v>
       </c>
-      <c r="B24" s="79" t="s">
-        <v>162</v>
-      </c>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79" t="s">
-        <v>163</v>
-      </c>
-      <c r="F24" s="79"/>
+      <c r="B24" s="85" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" s="85"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="85" t="s">
+        <v>160</v>
+      </c>
+      <c r="F24" s="85"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="85"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
+      <c r="B26" s="85"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="85"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="85"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="79"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="79"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
+      <c r="B28" s="85"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="85"/>
+      <c r="F28" s="85"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="79"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="85"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="79"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="85"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="85"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="79"/>
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="44"/>
     </row>
     <row r="34" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F34" s="64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G34" s="56">
         <f>COUNTA(G19:G33)</f>
@@ -7636,64 +7247,64 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="57" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E35" s="64"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="64" t="s">
-        <v>82</v>
-      </c>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
+        <v>79</v>
+      </c>
+      <c r="B36" s="78"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="78"/>
       <c r="E36" s="60" t="s">
-        <v>83</v>
-      </c>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
+        <v>80</v>
+      </c>
+      <c r="F36" s="78"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="78"/>
+      <c r="I36" s="78"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="64"/>
-      <c r="B37" s="66"/>
-      <c r="C37" s="66"/>
-      <c r="D37" s="66"/>
-      <c r="F37" s="66"/>
-      <c r="G37" s="66"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="66"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="64"/>
-      <c r="B38" s="66"/>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="66"/>
+      <c r="B38" s="76"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="76"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="64"/>
-      <c r="B39" s="66"/>
-      <c r="C39" s="66"/>
-      <c r="D39" s="66"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="66"/>
-      <c r="H39" s="66"/>
-      <c r="I39" s="66"/>
+      <c r="B39" s="76"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="76"/>
     </row>
     <row r="40" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E40" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -7701,52 +7312,6 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G5:H5"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="F38:I38"/>
     <mergeCell ref="B39:D39"/>
@@ -7763,6 +7328,52 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="F37:I37"/>
     <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{4C4DB9CF-C79C-4E5A-A850-965613BF762B}"/>
@@ -7794,459 +7405,459 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="88" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
+      <c r="B1" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="2" t="s">
-        <v>1</v>
+      <c r="I1" s="65" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="C2" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>9</v>
       </c>
       <c r="D3" s="7" t="d">
         <v>2026-06-30</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="78"/>
+      <c r="G3" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="69"/>
       <c r="I3" s="7"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
       <c r="C4" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="75" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" s="75"/>
+      <c r="G4" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="66"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" s="73"/>
+      <c r="G5" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="70"/>
       <c r="I5" s="54"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="89" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="89"/>
+        <v>22</v>
+      </c>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="87" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="87"/>
       <c r="I6" s="55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
+        <v>72</v>
+      </c>
+      <c r="B7" s="76"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="66"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="66"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
-      <c r="G9" s="66"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="66"/>
+        <v>73</v>
+      </c>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
+      <c r="B11" s="76"/>
+      <c r="C11" s="76"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="76"/>
+      <c r="I11" s="76"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="66"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="76"/>
+      <c r="I13" s="76"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
+      <c r="B14" s="76"/>
+      <c r="C14" s="76"/>
+      <c r="D14" s="76"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="76"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="82" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="71" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="85" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="85"/>
-      <c r="I16" s="85"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74" t="s">
-        <v>31</v>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="74"/>
-      <c r="B18" s="74"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
       <c r="G18" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="74"/>
+      <c r="I18" s="71"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="44">
         <v>1</v>
       </c>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="44"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="44"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="44"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="44"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="79"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="85"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="44"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="44"/>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="44"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="44"/>
-      <c r="B24" s="79"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="79"/>
+      <c r="B24" s="85"/>
+      <c r="C24" s="85"/>
+      <c r="D24" s="85"/>
+      <c r="E24" s="85"/>
+      <c r="F24" s="85"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="44"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="44"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="85"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="44"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="44"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
+      <c r="B26" s="85"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="85"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="85"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="44"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="44"/>
-      <c r="B27" s="79"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="79"/>
-      <c r="F27" s="79"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="44"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="44"/>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
+      <c r="B28" s="85"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="85"/>
+      <c r="F28" s="85"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="44"/>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="79"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="85"/>
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="44"/>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
+      <c r="B30" s="85"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="85"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="44"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="79"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="85"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="85"/>
+      <c r="D32" s="85"/>
+      <c r="E32" s="85"/>
+      <c r="F32" s="85"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="44"/>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="79"/>
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
+      <c r="F33" s="85"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="44"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="44"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="79"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="85"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="44"/>
     </row>
     <row r="35" spans="1:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F35" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G35" s="56">
         <f>COUNTA(G19:G34)</f>
@@ -8259,64 +7870,64 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="57" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68"/>
-      <c r="D37" s="68"/>
+        <v>79</v>
+      </c>
+      <c r="B37" s="78"/>
+      <c r="C37" s="78"/>
+      <c r="D37" s="78"/>
       <c r="E37" t="s">
-        <v>83</v>
-      </c>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
-      <c r="H37" s="68"/>
-      <c r="I37" s="68"/>
+        <v>80</v>
+      </c>
+      <c r="F37" s="78"/>
+      <c r="G37" s="78"/>
+      <c r="H37" s="78"/>
+      <c r="I37" s="78"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
-      <c r="B38" s="66"/>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="66"/>
+      <c r="B38" s="76"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="76"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
-      <c r="B39" s="66"/>
-      <c r="C39" s="66"/>
-      <c r="D39" s="66"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="66"/>
-      <c r="H39" s="66"/>
-      <c r="I39" s="66"/>
+      <c r="B39" s="76"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="76"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="66"/>
+      <c r="B40" s="76"/>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
+      <c r="I40" s="76"/>
     </row>
     <row r="41" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E41" s="58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8324,12 +7935,52 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:I18"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="B6:F6"/>
@@ -8342,52 +7993,12 @@
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:D18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:I39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I1" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
